--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
@@ -194,7 +194,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -204,12 +204,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -260,17 +254,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,97 +46,43 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
-  </si>
-  <si>
-    <t>1156 Добрич бул. Добруджа</t>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Добрич Добруджа</t>
+  </si>
+  <si>
+    <t>В5575XK</t>
+  </si>
+  <si>
+    <t>В6478ТМ</t>
   </si>
   <si>
     <t>ТУБАБ1</t>
   </si>
   <si>
-    <t>В5575XK</t>
+    <t>78970156027720491</t>
+  </si>
+  <si>
+    <t>78970153027721041</t>
   </si>
   <si>
     <t>78970153027721033</t>
   </si>
   <si>
-    <t>78970156027720491</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:59:00</t>
-  </si>
-  <si>
-    <t>09:09:00</t>
-  </si>
-  <si>
-    <t>19:58:00</t>
-  </si>
-  <si>
-    <t>09:36:00</t>
-  </si>
-  <si>
-    <t>13:25:00</t>
-  </si>
-  <si>
-    <t>08:50:00</t>
-  </si>
-  <si>
-    <t>09:26:00</t>
-  </si>
-  <si>
-    <t>12:30:00</t>
-  </si>
-  <si>
-    <t>14:13:00</t>
-  </si>
-  <si>
-    <t>3232030775 3232030775</t>
-  </si>
-  <si>
-    <t>3232151017 3232151017</t>
-  </si>
-  <si>
-    <t>3232192392 3232192392</t>
-  </si>
-  <si>
-    <t>3232236169 3232236169</t>
-  </si>
-  <si>
-    <t>3232243153 3232243153</t>
-  </si>
-  <si>
-    <t>3232400375 3232400375</t>
-  </si>
-  <si>
-    <t>3232568209 3232568209</t>
-  </si>
-  <si>
-    <t>3232586057 3232586057</t>
-  </si>
-  <si>
-    <t>3232578018 3232578018</t>
   </si>
   <si>
     <t>Общи литри по продукт / БКС ДОЛНИ ЧИФЛИК ЕООД</t>
@@ -559,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -568,17 +511,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -612,201 +552,156 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46160</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
       </c>
       <c r="F2">
-        <v>600</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
+        <v>60.16</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.51</v>
       </c>
       <c r="H2">
-        <v>1.64</v>
+        <v>90.84</v>
       </c>
       <c r="I2" s="1">
-        <v>984</v>
+        <v>1.57</v>
       </c>
       <c r="J2">
-        <v>1.75</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>94.45</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="3">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>990</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
+        <v>46</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.61</v>
       </c>
       <c r="H3">
-        <v>1.63</v>
+        <v>74.06</v>
       </c>
       <c r="I3" s="1">
-        <v>1613.7</v>
+        <v>1.69</v>
       </c>
       <c r="J3">
-        <v>1.75</v>
-      </c>
-      <c r="K3" s="1">
-        <v>1732.5</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>77.73999999999999</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="3">
-        <v>46163</v>
+        <v>46175</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
+        <v>900</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.61</v>
       </c>
       <c r="H4">
-        <v>1.63</v>
+        <v>1449</v>
       </c>
       <c r="I4" s="1">
-        <v>52.16</v>
+        <v>1.69</v>
       </c>
       <c r="J4">
-        <v>1.75</v>
-      </c>
-      <c r="K4" s="1">
-        <v>56</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>1521</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="3">
-        <v>46164</v>
+        <v>46177</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>800</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
+        <v>400</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.61</v>
       </c>
       <c r="H5">
-        <v>1.63</v>
+        <v>644</v>
       </c>
       <c r="I5" s="1">
-        <v>1304</v>
+        <v>1.66</v>
       </c>
       <c r="J5">
-        <v>1.74</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1392</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>664</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="3">
-        <v>46164</v>
+        <v>46177</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -815,300 +710,325 @@
         <v>22</v>
       </c>
       <c r="F6">
-        <v>56.08</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
+        <v>900</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.61</v>
       </c>
       <c r="H6">
-        <v>1.49</v>
+        <v>1449</v>
       </c>
       <c r="I6" s="1">
-        <v>83.56</v>
+        <v>1.66</v>
       </c>
       <c r="J6">
-        <v>1.57</v>
-      </c>
-      <c r="K6" s="1">
-        <v>88.05</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>1494</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="3">
-        <v>46168</v>
+        <v>46178</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>400</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
+        <v>990</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.61</v>
       </c>
       <c r="H7">
-        <v>1.63</v>
+        <v>1593.9</v>
       </c>
       <c r="I7" s="1">
-        <v>652</v>
+        <v>1.66</v>
       </c>
       <c r="J7">
-        <v>1.72</v>
-      </c>
-      <c r="K7" s="1">
-        <v>688</v>
-      </c>
-      <c r="L7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>1643.4</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="3">
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>500</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
+        <v>900</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.61</v>
       </c>
       <c r="H8">
-        <v>1.62</v>
+        <v>1449</v>
       </c>
       <c r="I8" s="1">
-        <v>810</v>
+        <v>1.64</v>
       </c>
       <c r="J8">
-        <v>1.7</v>
-      </c>
-      <c r="K8" s="1">
-        <v>850</v>
-      </c>
-      <c r="L8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>1476</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="3">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
       </c>
       <c r="F9">
-        <v>299.99</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
+        <v>59.81</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.51</v>
       </c>
       <c r="H9">
-        <v>1.62</v>
+        <v>90.31</v>
       </c>
       <c r="I9" s="1">
-        <v>485.98</v>
+        <v>1.56</v>
       </c>
       <c r="J9">
-        <v>1.7</v>
-      </c>
-      <c r="K9" s="1">
-        <v>509.98</v>
-      </c>
-      <c r="L9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>93.3</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="3">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
         <v>20</v>
       </c>
       <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10">
+        <v>800</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H10">
+        <v>1288</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="J10">
+        <v>1288</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11">
+        <v>36.43</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H11">
+        <v>58.65</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="J11">
+        <v>58.65</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12">
+        <v>600</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H12">
+        <v>966</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="J12">
+        <v>966</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="7">
+        <v>5572.43</v>
+      </c>
+      <c r="C17" s="7">
+        <v>9</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1.61</v>
+      </c>
+      <c r="E17" s="7">
+        <v>8971.610000000001</v>
+      </c>
+      <c r="F17" s="7">
+        <v>9188.790000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F10">
-        <v>39.17</v>
-      </c>
-      <c r="G10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10">
-        <v>1.62</v>
-      </c>
-      <c r="I10" s="1">
-        <v>63.46</v>
-      </c>
-      <c r="J10">
-        <v>1.7</v>
-      </c>
-      <c r="K10" s="1">
-        <v>66.59</v>
-      </c>
-      <c r="L10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="7">
-        <v>3661.16</v>
-      </c>
-      <c r="C15" s="7">
-        <v>8</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1.6293</v>
-      </c>
-      <c r="E15" s="7">
-        <v>5965.3</v>
-      </c>
-      <c r="F15" s="7">
-        <v>6345.07</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="7">
-        <v>56.08</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1</v>
-      </c>
-      <c r="D16" s="8">
-        <v>1.49</v>
-      </c>
-      <c r="E16" s="7">
-        <v>83.56</v>
-      </c>
-      <c r="F16" s="7">
-        <v>88.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="10">
-        <v>3717.24</v>
-      </c>
-      <c r="C17" s="10">
-        <v>9</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="10">
-        <v>6048.86</v>
-      </c>
-      <c r="F17" s="10">
-        <v>6433.12</v>
+      <c r="B18" s="7">
+        <v>119.97</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1.51</v>
+      </c>
+      <c r="E18" s="7">
+        <v>181.15</v>
+      </c>
+      <c r="F18" s="7">
+        <v>187.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="10">
+        <v>5692.4</v>
+      </c>
+      <c r="C19" s="10">
+        <v>11</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="10">
+        <v>9152.76</v>
+      </c>
+      <c r="F19" s="10">
+        <v>9376.540000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="57">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,13 +52,19 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Разград</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1197 Разград</t>
   </si>
   <si>
     <t>ТУБАБ1</t>
@@ -64,40 +73,100 @@
     <t>В5575XK</t>
   </si>
   <si>
+    <t>В6478ТМ</t>
+  </si>
+  <si>
     <t>78970153027721033</t>
   </si>
   <si>
     <t>78970156027720491</t>
   </si>
   <si>
+    <t>78970153027721041</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-16 09:04:24</t>
-  </si>
-  <si>
-    <t>2026-06-20 15:27:14</t>
-  </si>
-  <si>
-    <t>2026-06-22 08:48:21</t>
-  </si>
-  <si>
-    <t>2026-06-22 08:54:24</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:19:23</t>
-  </si>
-  <si>
-    <t>2026-06-25 08:40:05</t>
-  </si>
-  <si>
-    <t>2026-06-25 08:45:43</t>
-  </si>
-  <si>
-    <t>2026-06-25 12:19:35</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:04:00</t>
+  </si>
+  <si>
+    <t>15:26:00</t>
+  </si>
+  <si>
+    <t>08:48:00</t>
+  </si>
+  <si>
+    <t>08:54:00</t>
+  </si>
+  <si>
+    <t>12:20:00</t>
+  </si>
+  <si>
+    <t>08:40:00</t>
+  </si>
+  <si>
+    <t>08:45:00</t>
+  </si>
+  <si>
+    <t>13:58:00</t>
+  </si>
+  <si>
+    <t>17:23:00</t>
+  </si>
+  <si>
+    <t>08:51:00</t>
+  </si>
+  <si>
+    <t>12:41:00</t>
+  </si>
+  <si>
+    <t>09:17:00</t>
+  </si>
+  <si>
+    <t>3233426071 3233426071</t>
+  </si>
+  <si>
+    <t>3233628669 3233628669</t>
+  </si>
+  <si>
+    <t>3233677384 3233677384</t>
+  </si>
+  <si>
+    <t>3233694077 3233694077</t>
+  </si>
+  <si>
+    <t>3233723292 3233723292</t>
+  </si>
+  <si>
+    <t>3233788970 3233788970</t>
+  </si>
+  <si>
+    <t>3233851227 3233851227</t>
+  </si>
+  <si>
+    <t>3233865372 3233865372</t>
+  </si>
+  <si>
+    <t>3233920047 3233920047</t>
+  </si>
+  <si>
+    <t>3234057529 3234057529</t>
+  </si>
+  <si>
+    <t>3234094963 3234094963</t>
+  </si>
+  <si>
+    <t>3234116015 3234116015</t>
+  </si>
+  <si>
+    <t>3234096204 3234096204</t>
   </si>
   <si>
     <t>Общи литри по продукт / БКС ДОЛНИ ЧИФЛИК ЕООД</t>
@@ -517,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -526,14 +595,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,378 +639,679 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>800</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
         <v>1.55</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>1240</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.59</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1272</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46193</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>57.83</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3">
         <v>1.43</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>82.7</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.53</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>88.48</v>
       </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46195</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>900</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
         <v>1.47</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>1323</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.52</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>1368</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46195</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>61.02</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5">
         <v>1.47</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>89.7</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.52</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>92.75</v>
       </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46195</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>700</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6">
         <v>1.47</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>1029</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.52</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>1064</v>
       </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46198</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>700</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7">
         <v>1.46</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>1022</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.51</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>1057</v>
       </c>
-      <c r="K7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46198</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F8">
         <v>200</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8">
         <v>1.46</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>292</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.51</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>302</v>
       </c>
-      <c r="K8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46198</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F9">
         <v>900</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9">
         <v>1.46</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>1314</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.51</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>1359</v>
       </c>
-      <c r="K9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="L9" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="6" t="s">
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10">
+        <v>43.6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10">
+        <v>1.44</v>
+      </c>
+      <c r="I10" s="1">
+        <v>62.78</v>
+      </c>
+      <c r="J10">
+        <v>1.51</v>
+      </c>
+      <c r="K10" s="1">
+        <v>65.84</v>
+      </c>
+      <c r="L10" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="7">
-        <v>4261.02</v>
-      </c>
-      <c r="C14" s="7">
-        <v>7</v>
-      </c>
-      <c r="D14" s="8">
-        <v>1.4808</v>
-      </c>
-      <c r="E14" s="7">
-        <v>6309.7</v>
-      </c>
-      <c r="F14" s="7">
-        <v>6514.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="7">
-        <v>57.83</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1.4301</v>
-      </c>
-      <c r="E15" s="7">
-        <v>82.7</v>
-      </c>
-      <c r="F15" s="7">
-        <v>88.48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="10">
-        <v>4318.85</v>
-      </c>
-      <c r="C16" s="10">
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11">
+        <v>41.54</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11">
+        <v>1.43</v>
+      </c>
+      <c r="I11" s="1">
+        <v>59.4</v>
+      </c>
+      <c r="J11">
+        <v>1.51</v>
+      </c>
+      <c r="K11" s="1">
+        <v>62.73</v>
+      </c>
+      <c r="L11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12">
+        <v>700.0700000000001</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <v>1.43</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1001.1</v>
+      </c>
+      <c r="J12">
+        <v>1.51</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1057.11</v>
+      </c>
+      <c r="L12" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>900</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <v>1.43</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1287</v>
+      </c>
+      <c r="J13">
+        <v>1.51</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1359</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14">
+        <v>59.63</v>
+      </c>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14">
+        <v>1.39</v>
+      </c>
+      <c r="I14" s="1">
+        <v>82.89</v>
+      </c>
+      <c r="J14">
+        <v>1.5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>89.44</v>
+      </c>
+      <c r="L14" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="10">
-        <v>6392.4</v>
-      </c>
-      <c r="F16" s="10">
-        <v>6603.23</v>
+      <c r="F18" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="7">
+        <v>5946.23</v>
+      </c>
+      <c r="C19" s="7">
+        <v>11</v>
+      </c>
+      <c r="D19" s="8">
+        <v>1.4665</v>
+      </c>
+      <c r="E19" s="7">
+        <v>8719.98</v>
+      </c>
+      <c r="F19" s="7">
+        <v>9059.43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="7">
+        <v>117.46</v>
+      </c>
+      <c r="C20" s="7">
+        <v>2</v>
+      </c>
+      <c r="D20" s="8">
+        <v>1.4098</v>
+      </c>
+      <c r="E20" s="7">
+        <v>165.59</v>
+      </c>
+      <c r="F20" s="7">
+        <v>177.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="10">
+        <v>6063.69</v>
+      </c>
+      <c r="C21" s="10">
+        <v>13</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="10">
+        <v>8885.57</v>
+      </c>
+      <c r="F21" s="10">
+        <v>9237.35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="58">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,16 +55,22 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Разград</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Тракия Езеро</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1197 Разград</t>
+  </si>
+  <si>
+    <t>В5575XK</t>
   </si>
   <si>
     <t>ТУБАБ1</t>
@@ -70,46 +79,97 @@
     <t>В5454ХМ</t>
   </si>
   <si>
+    <t>78970156027720491</t>
+  </si>
+  <si>
     <t>78970153027721033</t>
   </si>
   <si>
     <t>78970151027721060</t>
   </si>
   <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
-  </si>
-  <si>
-    <t>2026-07-02 09:19:22</t>
-  </si>
-  <si>
-    <t>2026-07-06 09:48:11</t>
-  </si>
-  <si>
-    <t>2026-07-08 11:08:53</t>
-  </si>
-  <si>
-    <t>2026-07-11 13:21:57</t>
-  </si>
-  <si>
-    <t>2026-07-12 16:16:17</t>
-  </si>
-  <si>
-    <t>2026-07-12 16:16:18</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:36:41</t>
-  </si>
-  <si>
-    <t>2026-07-14 19:04:34</t>
-  </si>
-  <si>
-    <t>2026-07-15 09:06:06</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:04:00</t>
+  </si>
+  <si>
+    <t>09:05:00</t>
+  </si>
+  <si>
+    <t>09:45:00</t>
+  </si>
+  <si>
+    <t>19:47:00</t>
+  </si>
+  <si>
+    <t>18:33:00</t>
+  </si>
+  <si>
+    <t>09:20:00</t>
+  </si>
+  <si>
+    <t>11:59:00</t>
+  </si>
+  <si>
+    <t>12:56:00</t>
+  </si>
+  <si>
+    <t>13:29:00</t>
+  </si>
+  <si>
+    <t>09:32:00</t>
+  </si>
+  <si>
+    <t>09:26:00</t>
+  </si>
+  <si>
+    <t>14:26:00</t>
+  </si>
+  <si>
+    <t>3234882247 3234882247</t>
+  </si>
+  <si>
+    <t>3234894995 3234894995</t>
+  </si>
+  <si>
+    <t>3235088906 3235088906</t>
+  </si>
+  <si>
+    <t>3235121464 3235121464</t>
+  </si>
+  <si>
+    <t>3235144846 3235144846</t>
+  </si>
+  <si>
+    <t>3235157358 3235157358</t>
+  </si>
+  <si>
+    <t>3235283493 3235283493</t>
+  </si>
+  <si>
+    <t>3235322067 3235322067</t>
+  </si>
+  <si>
+    <t>3235431804 3235431804</t>
+  </si>
+  <si>
+    <t>3235475495 3235475495</t>
+  </si>
+  <si>
+    <t>3235570331 3235570331</t>
+  </si>
+  <si>
+    <t>3235594938 3235594938</t>
   </si>
   <si>
     <t>Общи литри по продукт / БКС ДОЛНИ ЧИФЛИК ЕООД</t>
@@ -529,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -538,15 +598,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -583,460 +645,652 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46205</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2">
+        <v>58.95</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
+        <v>1.4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>82.53</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>88.43000000000001</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3">
+        <v>750</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
+        <v>1.53</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1147.5</v>
+      </c>
+      <c r="J3">
+        <v>1.63</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1222.5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46223</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>450</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4">
+        <v>1.58</v>
+      </c>
+      <c r="I4" s="1">
+        <v>711</v>
+      </c>
+      <c r="J4">
+        <v>1.68</v>
+      </c>
+      <c r="K4" s="1">
+        <v>756</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5">
+        <v>67.47</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5">
+        <v>1.79</v>
+      </c>
+      <c r="I5" s="1">
+        <v>120.77</v>
+      </c>
+      <c r="J5">
+        <v>1.79</v>
+      </c>
+      <c r="K5" s="1">
+        <v>120.77</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <v>990</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="H2">
-        <v>1415.7</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J2">
-        <v>1494.9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2">
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>41.3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6">
+        <v>1.59</v>
+      </c>
+      <c r="I6" s="1">
+        <v>65.67</v>
+      </c>
+      <c r="J6">
+        <v>1.69</v>
+      </c>
+      <c r="K6" s="1">
+        <v>69.8</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46209</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>990</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="H3">
-        <v>1425.6</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J3">
-        <v>1504.8</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46211</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>999</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="H4">
-        <v>1438.56</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J4">
-        <v>1518.48</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>46214</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>44.81</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="H5">
-        <v>78.42</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="J5">
-        <v>78.42</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3">
-        <v>46215</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>90.02</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H6">
-        <v>159.34</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="J6">
-        <v>159.34</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="N6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
-        <v>46215</v>
+        <v>46225</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>450</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <v>1.62</v>
+      </c>
+      <c r="I7" s="1">
+        <v>729</v>
+      </c>
+      <c r="J7">
+        <v>1.69</v>
+      </c>
+      <c r="K7" s="1">
+        <v>760.5</v>
+      </c>
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>5.49</v>
-      </c>
-      <c r="H7">
-        <v>5.49</v>
-      </c>
-      <c r="I7" s="1">
-        <v>5.49</v>
-      </c>
-      <c r="J7">
-        <v>5.49</v>
-      </c>
-      <c r="K7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="3">
-        <v>46216</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>990</v>
       </c>
-      <c r="G8" s="1">
-        <v>1.48</v>
+      <c r="G8" t="s">
+        <v>27</v>
       </c>
       <c r="H8">
-        <v>1465.2</v>
+        <v>1.65</v>
       </c>
       <c r="I8" s="1">
+        <v>1633.5</v>
+      </c>
+      <c r="J8">
+        <v>1.72</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1702.8</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3">
+        <v>46228</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9">
+        <v>56.39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9">
+        <v>1.81</v>
+      </c>
+      <c r="I9" s="1">
+        <v>102.07</v>
+      </c>
+      <c r="J9">
+        <v>1.81</v>
+      </c>
+      <c r="K9" s="1">
+        <v>102.07</v>
+      </c>
+      <c r="L9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3">
+        <v>46230</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10">
+        <v>60.94</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10">
+        <v>1.44</v>
+      </c>
+      <c r="I10" s="1">
+        <v>87.75</v>
+      </c>
+      <c r="J10">
         <v>1.56</v>
       </c>
-      <c r="J8">
-        <v>1544.4</v>
-      </c>
-      <c r="K8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8">
+      <c r="K10" s="1">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="N10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11">
+        <v>600</v>
+      </c>
+      <c r="G11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11">
+        <v>1.68</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1008</v>
+      </c>
+      <c r="J11">
+        <v>1.75</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1050</v>
+      </c>
+      <c r="L11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12">
+        <v>400</v>
+      </c>
+      <c r="G12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12">
+        <v>1.7</v>
+      </c>
+      <c r="I12" s="1">
+        <v>680</v>
+      </c>
+      <c r="J12">
+        <v>1.76</v>
+      </c>
+      <c r="K12" s="1">
+        <v>704</v>
+      </c>
+      <c r="L12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9">
-        <v>62.24</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="H9">
-        <v>108.92</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="J9">
-        <v>108.92</v>
-      </c>
-      <c r="K9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9">
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13">
+        <v>400.01</v>
+      </c>
+      <c r="G13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13">
+        <v>1.7</v>
+      </c>
+      <c r="I13" s="1">
+        <v>680.02</v>
+      </c>
+      <c r="J13">
+        <v>1.76</v>
+      </c>
+      <c r="K13" s="1">
+        <v>704.02</v>
+      </c>
+      <c r="L13" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="3">
-        <v>46218</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="N13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7">
+        <v>4081.31</v>
+      </c>
+      <c r="C18" s="7">
+        <v>8</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1.6305</v>
+      </c>
+      <c r="E18" s="7">
+        <v>6654.69</v>
+      </c>
+      <c r="F18" s="7">
+        <v>6969.62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="7">
+        <v>123.86</v>
+      </c>
+      <c r="C19" s="7">
+        <v>2</v>
+      </c>
+      <c r="D19" s="8">
+        <v>1.7991</v>
+      </c>
+      <c r="E19" s="7">
+        <v>222.84</v>
+      </c>
+      <c r="F19" s="7">
+        <v>222.84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="7">
+        <v>119.89</v>
+      </c>
+      <c r="C20" s="7">
+        <v>2</v>
+      </c>
+      <c r="D20" s="8">
+        <v>1.4203</v>
+      </c>
+      <c r="E20" s="7">
+        <v>170.28</v>
+      </c>
+      <c r="F20" s="7">
+        <v>183.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="10">
+        <v>4325.06</v>
+      </c>
+      <c r="C21" s="10">
         <v>12</v>
       </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10">
-        <v>990</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H10">
-        <v>1504.8</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J10">
-        <v>1564.2</v>
-      </c>
-      <c r="K10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="7">
-        <v>4959</v>
-      </c>
-      <c r="C15" s="7">
-        <v>5</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1.462</v>
-      </c>
-      <c r="E15" s="7">
-        <v>7249.86</v>
-      </c>
-      <c r="F15" s="7">
-        <v>7626.78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="7">
-        <v>197.07</v>
-      </c>
-      <c r="C16" s="7">
-        <v>3</v>
-      </c>
-      <c r="D16" s="8">
-        <v>1.7592</v>
-      </c>
-      <c r="E16" s="7">
-        <v>346.68</v>
-      </c>
-      <c r="F16" s="7">
-        <v>346.68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="7">
-        <v>1</v>
-      </c>
-      <c r="C17" s="7">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8">
-        <v>5.49</v>
-      </c>
-      <c r="E17" s="7">
-        <v>5.49</v>
-      </c>
-      <c r="F17" s="7">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="10">
-        <v>5157.07</v>
-      </c>
-      <c r="C18" s="10">
-        <v>9</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="10">
-        <v>7602.03</v>
-      </c>
-      <c r="F18" s="10">
-        <v>7978.95</v>
+      <c r="D21" s="8"/>
+      <c r="E21" s="10">
+        <v>7047.81</v>
+      </c>
+      <c r="F21" s="10">
+        <v>7375.96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
@@ -197,7 +197,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1221,7 +1221,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="8">
-        <v>1.6305</v>
+        <v>1.630528</v>
       </c>
       <c r="E18" s="7">
         <v>6654.69</v>
@@ -1241,7 +1241,7 @@
         <v>2</v>
       </c>
       <c r="D19" s="8">
-        <v>1.7991</v>
+        <v>1.799128</v>
       </c>
       <c r="E19" s="7">
         <v>222.84</v>
@@ -1261,7 +1261,7 @@
         <v>2</v>
       </c>
       <c r="D20" s="8">
-        <v>1.4203</v>
+        <v>1.420302</v>
       </c>
       <c r="E20" s="7">
         <v>170.28</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="59">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -589,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -602,13 +605,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -651,538 +654,577 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>58.95</v>
+        <v>58.953</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>1.369</v>
       </c>
       <c r="I2" s="1">
-        <v>82.53</v>
+        <v>1.399</v>
       </c>
       <c r="J2">
+        <v>82.475247</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.5</v>
       </c>
-      <c r="K2" s="1">
-        <v>88.43000000000001</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>88.4295</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3">
         <v>750</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3">
-        <v>1.53</v>
+        <v>1.499</v>
       </c>
       <c r="I3" s="1">
-        <v>1147.5</v>
+        <v>1.529</v>
       </c>
       <c r="J3">
+        <v>1146.75</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.63</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>1222.5</v>
       </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3">
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46223</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>450</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>1.58</v>
+        <v>1.546</v>
       </c>
       <c r="I4" s="1">
-        <v>711</v>
+        <v>1.576</v>
       </c>
       <c r="J4">
+        <v>709.2</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.68</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>756</v>
       </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4">
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46224</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>67.47</v>
+        <v>67.46899999999999</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5">
         <v>1.79</v>
       </c>
       <c r="I5" s="1">
-        <v>120.77</v>
+        <v>1.79</v>
       </c>
       <c r="J5">
+        <v>120.76951</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.79</v>
       </c>
-      <c r="K5" s="1">
-        <v>120.77</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>120.76951</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46224</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>41.3</v>
+        <v>41.302</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>1.59</v>
+        <v>1.564</v>
       </c>
       <c r="I6" s="1">
-        <v>65.67</v>
+        <v>1.594</v>
       </c>
       <c r="J6">
+        <v>65.83538799999999</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.69</v>
       </c>
-      <c r="K6" s="1">
-        <v>69.8</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>69.80038</v>
+      </c>
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46225</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>450</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7">
-        <v>1.62</v>
+        <v>1.588</v>
       </c>
       <c r="I7" s="1">
-        <v>729</v>
+        <v>1.618</v>
       </c>
       <c r="J7">
+        <v>728.1</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.69</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>760.5</v>
       </c>
-      <c r="L7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7">
+      <c r="M7" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46227</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>990</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H8">
-        <v>1.65</v>
+        <v>1.619</v>
       </c>
       <c r="I8" s="1">
-        <v>1633.5</v>
+        <v>1.649</v>
       </c>
       <c r="J8">
+        <v>1632.51</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.72</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>1702.8</v>
       </c>
-      <c r="L8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8">
+      <c r="M8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46228</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>56.39</v>
+        <v>56.392</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9">
         <v>1.81</v>
       </c>
       <c r="I9" s="1">
-        <v>102.07</v>
+        <v>1.81</v>
       </c>
       <c r="J9">
+        <v>102.06952</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.81</v>
       </c>
-      <c r="K9" s="1">
-        <v>102.07</v>
-      </c>
-      <c r="L9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>102.06952</v>
+      </c>
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46230</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>60.94</v>
+        <v>60.942</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10">
-        <v>1.44</v>
+        <v>1.401</v>
       </c>
       <c r="I10" s="1">
-        <v>87.75</v>
+        <v>1.441</v>
       </c>
       <c r="J10">
+        <v>87.81742199999999</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.56</v>
       </c>
-      <c r="K10" s="1">
-        <v>95.06999999999999</v>
-      </c>
-      <c r="L10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>95.06952</v>
+      </c>
+      <c r="M10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46231</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11">
         <v>600</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H11">
-        <v>1.68</v>
+        <v>1.653</v>
       </c>
       <c r="I11" s="1">
-        <v>1008</v>
+        <v>1.683</v>
       </c>
       <c r="J11">
+        <v>1009.8</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.75</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>1050</v>
       </c>
-      <c r="L11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M11">
+      <c r="M11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46233</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12">
         <v>400</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H12">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I12" s="1">
-        <v>680</v>
+        <v>1.704</v>
       </c>
       <c r="J12">
+        <v>681.6</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.76</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>704</v>
       </c>
-      <c r="L12" t="s">
-        <v>38</v>
-      </c>
-      <c r="M12">
+      <c r="M12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46233</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13">
-        <v>400.01</v>
+        <v>400.011</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H13">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I13" s="1">
-        <v>680.02</v>
+        <v>1.704</v>
       </c>
       <c r="J13">
+        <v>681.618744</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.76</v>
       </c>
-      <c r="K13" s="1">
-        <v>704.02</v>
-      </c>
-      <c r="L13" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>704.01936</v>
+      </c>
+      <c r="M13" t="s">
+        <v>40</v>
+      </c>
+      <c r="N13">
         <v>0</v>
       </c>
-      <c r="N13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1192,39 +1234,39 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="7">
-        <v>4081.31</v>
+        <v>4081.313</v>
       </c>
       <c r="C18" s="7">
         <v>8</v>
       </c>
       <c r="D18" s="8">
-        <v>1.630528</v>
+        <v>1.630704</v>
       </c>
       <c r="E18" s="7">
-        <v>6654.69</v>
+        <v>6655.41</v>
       </c>
       <c r="F18" s="7">
         <v>6969.62</v>
@@ -1232,16 +1274,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="7">
-        <v>123.86</v>
+        <v>123.861</v>
       </c>
       <c r="C19" s="7">
         <v>2</v>
       </c>
       <c r="D19" s="8">
-        <v>1.799128</v>
+        <v>1.799106</v>
       </c>
       <c r="E19" s="7">
         <v>222.84</v>
@@ -1252,19 +1294,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="7">
-        <v>119.89</v>
+        <v>119.895</v>
       </c>
       <c r="C20" s="7">
         <v>2</v>
       </c>
       <c r="D20" s="8">
-        <v>1.420302</v>
+        <v>1.420348</v>
       </c>
       <c r="E20" s="7">
-        <v>170.28</v>
+        <v>170.29</v>
       </c>
       <c r="F20" s="7">
         <v>183.5</v>
@@ -1272,17 +1314,17 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="10">
-        <v>4325.06</v>
+        <v>4325.069</v>
       </c>
       <c r="C21" s="10">
         <v>12</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="10">
-        <v>7047.81</v>
+        <v>7048.54</v>
       </c>
       <c r="F21" s="10">
         <v>7375.96</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/БКС ДОЛНИ ЧИФЛИК ЕООД/БКС ДОЛНИ ЧИФЛИК ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="58">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -198,9 +195,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -294,10 +291,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -592,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -605,13 +602,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -654,577 +651,538 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>58.953</v>
       </c>
       <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
+        <v>82.47499999999999</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>88.43000000000001</v>
+      </c>
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="H2">
-        <v>1.369</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.399</v>
-      </c>
-      <c r="J2">
-        <v>82.475247</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>88.4295</v>
-      </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>750</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I3" s="1">
-        <v>1.529</v>
+        <v>1146.75</v>
       </c>
       <c r="J3">
-        <v>1146.75</v>
+        <v>1.63</v>
       </c>
       <c r="K3" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L3" s="1">
         <v>1222.5</v>
       </c>
-      <c r="M3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46223</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>450</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4">
-        <v>1.546</v>
+        <v>1.576</v>
       </c>
       <c r="I4" s="1">
-        <v>1.576</v>
+        <v>709.2</v>
       </c>
       <c r="J4">
-        <v>709.2</v>
+        <v>1.68</v>
       </c>
       <c r="K4" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L4" s="1">
         <v>756</v>
       </c>
-      <c r="M4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46224</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>67.46899999999999</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5">
         <v>1.79</v>
       </c>
       <c r="I5" s="1">
+        <v>120.77</v>
+      </c>
+      <c r="J5">
         <v>1.79</v>
       </c>
-      <c r="J5">
-        <v>120.76951</v>
-      </c>
       <c r="K5" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L5" s="1">
-        <v>120.76951</v>
-      </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5">
+        <v>120.77</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46224</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>41.302</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I6" s="1">
-        <v>1.594</v>
+        <v>65.83499999999999</v>
       </c>
       <c r="J6">
-        <v>65.83538799999999</v>
+        <v>1.69</v>
       </c>
       <c r="K6" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L6" s="1">
-        <v>69.80038</v>
-      </c>
-      <c r="M6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6">
+        <v>69.8</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46225</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>450</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H7">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I7" s="1">
-        <v>1.618</v>
+        <v>728.1</v>
       </c>
       <c r="J7">
-        <v>728.1</v>
+        <v>1.69</v>
       </c>
       <c r="K7" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L7" s="1">
         <v>760.5</v>
       </c>
-      <c r="M7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7">
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46227</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>990</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I8" s="1">
-        <v>1.649</v>
+        <v>1632.51</v>
       </c>
       <c r="J8">
-        <v>1632.51</v>
+        <v>1.72</v>
       </c>
       <c r="K8" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L8" s="1">
         <v>1702.8</v>
       </c>
-      <c r="M8" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8">
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46228</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9">
         <v>56.392</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H9">
         <v>1.81</v>
       </c>
       <c r="I9" s="1">
+        <v>102.07</v>
+      </c>
+      <c r="J9">
         <v>1.81</v>
       </c>
-      <c r="J9">
-        <v>102.06952</v>
-      </c>
       <c r="K9" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L9" s="1">
-        <v>102.06952</v>
-      </c>
-      <c r="M9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N9">
+        <v>102.07</v>
+      </c>
+      <c r="L9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46230</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10">
         <v>60.942</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I10" s="1">
-        <v>1.441</v>
+        <v>87.81699999999999</v>
       </c>
       <c r="J10">
-        <v>87.81742199999999</v>
+        <v>1.56</v>
       </c>
       <c r="K10" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L10" s="1">
-        <v>95.06952</v>
-      </c>
-      <c r="M10" t="s">
-        <v>37</v>
-      </c>
-      <c r="N10">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46231</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11">
         <v>600</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H11">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I11" s="1">
-        <v>1.683</v>
+        <v>1009.8</v>
       </c>
       <c r="J11">
-        <v>1009.8</v>
+        <v>1.75</v>
       </c>
       <c r="K11" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L11" s="1">
         <v>1050</v>
       </c>
-      <c r="M11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N11">
+      <c r="L11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46233</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12">
         <v>400</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H12">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I12" s="1">
-        <v>1.704</v>
+        <v>681.6</v>
       </c>
       <c r="J12">
-        <v>681.6</v>
+        <v>1.76</v>
       </c>
       <c r="K12" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L12" s="1">
         <v>704</v>
       </c>
-      <c r="M12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12">
+      <c r="L12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12">
         <v>0</v>
       </c>
-      <c r="O12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46233</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13">
         <v>400.011</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H13">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I13" s="1">
-        <v>1.704</v>
+        <v>681.619</v>
       </c>
       <c r="J13">
-        <v>681.618744</v>
+        <v>1.76</v>
       </c>
       <c r="K13" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L13" s="1">
-        <v>704.01936</v>
-      </c>
-      <c r="M13" t="s">
-        <v>40</v>
-      </c>
-      <c r="N13">
+        <v>704.019</v>
+      </c>
+      <c r="L13" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-      <c r="O13" t="s">
+      <c r="N13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="4" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1234,87 +1192,87 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="7">
         <v>4081.313</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <v>8</v>
       </c>
       <c r="D18" s="8">
-        <v>1.630704</v>
-      </c>
-      <c r="E18" s="7">
-        <v>6655.41</v>
-      </c>
-      <c r="F18" s="7">
-        <v>6969.62</v>
+        <v>1.631</v>
+      </c>
+      <c r="E18" s="8">
+        <v>6655.414</v>
+      </c>
+      <c r="F18" s="8">
+        <v>6969.619</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="7">
         <v>123.861</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>2</v>
       </c>
       <c r="D19" s="8">
-        <v>1.799106</v>
-      </c>
-      <c r="E19" s="7">
+        <v>1.799</v>
+      </c>
+      <c r="E19" s="8">
         <v>222.84</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <v>222.84</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="7">
         <v>119.895</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>2</v>
       </c>
       <c r="D20" s="8">
-        <v>1.420348</v>
-      </c>
-      <c r="E20" s="7">
-        <v>170.29</v>
-      </c>
-      <c r="F20" s="7">
+        <v>1.42</v>
+      </c>
+      <c r="E20" s="8">
+        <v>170.292</v>
+      </c>
+      <c r="F20" s="8">
         <v>183.5</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" s="10">
         <v>4325.069</v>
@@ -1324,10 +1282,10 @@
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="10">
-        <v>7048.54</v>
+        <v>7048.546</v>
       </c>
       <c r="F21" s="10">
-        <v>7375.96</v>
+        <v>7375.959</v>
       </c>
     </row>
   </sheetData>
